--- a/data/administracion_de_tribunales/OP_LEY148Denegadas.xlsx
+++ b/data/administracion_de_tribunales/OP_LEY148Denegadas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEA07A3-78D8-45EF-B9A1-04B175E39E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0634D44-8BDD-47B0-AA80-E1BF393E490D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="22">
   <si>
     <t>Región</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t xml:space="preserve">Caguas </t>
+  </si>
+  <si>
+    <t>No ha lugar archivo de petición</t>
   </si>
 </sst>
 </file>
@@ -421,14 +424,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="4" max="5" width="35.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,18 +442,24 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -460,8 +469,11 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -471,8 +483,11 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -483,10 +498,13 @@
         <v>1</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -496,11 +514,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -508,60 +529,84 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -574,11 +619,15 @@
         <v>4</v>
       </c>
       <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v>4</v>
+        <f>SUM(D2:D14)</f>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>SUM(E3:E14)</f>
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
         <v>5</v>
       </c>
     </row>
@@ -589,14 +638,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="4" max="5" width="35.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,18 +656,24 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -626,15 +681,21 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -644,8 +705,11 @@
       <c r="C5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -655,19 +719,25 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -675,30 +745,45 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -706,13 +791,16 @@
         <v>3</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -720,10 +808,13 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -736,11 +827,15 @@
         <v>4</v>
       </c>
       <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v>4</v>
+        <f>SUM(D2:D14)</f>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>SUM(E3:E14)</f>
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
         <v>3</v>
       </c>
     </row>
@@ -751,15 +846,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.44140625" customWidth="1"/>
     <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="4" max="5" width="35.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -770,28 +865,40 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -801,24 +908,33 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -828,24 +944,33 @@
       <c r="C8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -853,21 +978,27 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -875,24 +1006,30 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -905,11 +1042,15 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v>2</v>
+        <f>SUM(D2:D14)</f>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>SUM(E3:E14)</f>
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
         <v>6</v>
       </c>
     </row>
@@ -920,14 +1061,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="4" max="5" width="35.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -938,28 +1079,40 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -969,8 +1122,11 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -981,43 +1137,64 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -1027,13 +1204,19 @@
       <c r="C13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1046,11 +1229,15 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v>2</v>
+        <f>SUM(D2:D14)</f>
+        <v>0</v>
       </c>
       <c r="E15">
         <f>SUM(E3:E14)</f>
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <f>SUM(F3:F14)</f>
         <v>1</v>
       </c>
     </row>
@@ -1061,14 +1248,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2A9B8A-292C-45E7-8351-57F72AFCC6AF}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="42.109375" customWidth="1"/>
     <col min="4" max="4" width="35.44140625" customWidth="1"/>
+    <col min="5" max="5" width="42.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1079,48 +1267,96 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1128,38 +1364,59 @@
         <v>6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1169,78 +1426,139 @@
       <c r="C9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15">
-        <f>SUM(B3:B14)</f>
-        <v>20</v>
+        <f>SUM(B2:B14)</f>
+        <v>62</v>
       </c>
       <c r="C15">
-        <f>SUM(C3:C14)</f>
-        <v>6</v>
+        <f>SUM(C2:C14)</f>
+        <v>5</v>
       </c>
       <c r="D15">
-        <f>SUM(D3:D14)</f>
-        <v>8</v>
+        <f>SUM(D2:D14)</f>
+        <v>1</v>
       </c>
       <c r="E15">
-        <f>SUM(E3:E14)</f>
-        <v>6</v>
+        <f>SUM(E2:E14)</f>
+        <v>51</v>
+      </c>
+      <c r="F15">
+        <f>SUM(F2:F14)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
